--- a/front/src/assets/emptyTemplate_.xlsx
+++ b/front/src/assets/emptyTemplate_.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10309"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE9F16A-12BD-0241-BA9F-9EA3B5CDADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B998F4D1-4B19-344E-BDF2-4F3841F53B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -172,17 +172,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -565,39 +590,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
       <c r="I2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -635,6 +660,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:H500">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>LEFT(A1,6)="Total "</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -646,24 +676,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -679,24 +709,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -712,24 +742,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -745,24 +775,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -778,24 +808,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -811,24 +841,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -844,24 +874,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -877,24 +907,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -910,24 +940,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -943,24 +973,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -976,24 +1006,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1009,24 +1039,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1042,24 +1072,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1075,24 +1105,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1108,24 +1138,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1141,24 +1171,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1174,24 +1204,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1207,24 +1237,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1240,24 +1270,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1273,24 +1303,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1306,24 +1336,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1339,24 +1369,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1372,24 +1402,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1405,24 +1435,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1438,24 +1468,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1471,24 +1501,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1504,24 +1534,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1537,24 +1567,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1570,24 +1600,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1603,24 +1633,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1636,24 +1666,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1669,24 +1699,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1702,24 +1732,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1735,24 +1765,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1768,24 +1798,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1801,24 +1831,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1834,24 +1864,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1867,24 +1897,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1900,24 +1930,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1933,24 +1963,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1966,24 +1996,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1999,24 +2029,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2032,24 +2062,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2065,24 +2095,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2098,24 +2128,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2131,24 +2161,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2164,24 +2194,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2197,24 +2227,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2230,24 +2260,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
